--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 02,07,26 лгрсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 02,07,26 лгрсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0635EAD6-E4A1-4CE0-B5A2-57540E7BA197}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50682E4A-CBB9-415E-BE61-11221F8BC4FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -192,9 +192,6 @@
     <t>Готовые чебупели сочные с мясом ТМ Горячая штучка флоу-пак 0,48 кг XXL  Поком</t>
   </si>
   <si>
-    <t>нужно увеличить продажи</t>
-  </si>
-  <si>
     <t>Готовые чебуреки с мясом ТМ Горячая штучка 0,09 кг флоу-пак ПОКОМ</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   <si>
     <t>Чебуреки сочные, ВЕС, куриные жарен. зам  ПОКОМ</t>
   </si>
+  <si>
+    <t>на остатках 0 (инфа со склада)</t>
+  </si>
 </sst>
 </file>
 
@@ -484,7 +484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -503,7 +503,6 @@
     <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
@@ -6794,7 +6793,7 @@
       </c>
       <c r="F5" s="3">
         <f>SUM(F6:F498)</f>
-        <v>15434.5</v>
+        <v>14603.5</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="16"/>
@@ -6826,11 +6825,11 @@
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>15304.359999999997</v>
+        <v>15847.559999999998</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
-        <v>15737.4</v>
+        <v>16241.4</v>
       </c>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
@@ -6861,22 +6860,22 @@
       <c r="AA5" s="16"/>
       <c r="AB5" s="3">
         <f>SUM(AB6:AB498)</f>
-        <v>6210.0120000000006</v>
+        <v>6318.652</v>
       </c>
       <c r="AC5" s="6"/>
       <c r="AD5" s="10">
         <f>SUM(AD6:AD498)</f>
-        <v>1654</v>
+        <v>1696</v>
       </c>
       <c r="AE5" s="3">
         <f>SUM(AE6:AE498)</f>
-        <v>6339.1199999999981</v>
+        <v>6439.9199999999992</v>
       </c>
       <c r="AF5" s="16"/>
       <c r="AG5" s="16"/>
       <c r="AH5" s="10">
         <f>SUM(AH6:AH498)</f>
-        <v>19.164285714285715</v>
+        <v>19.764285714285709</v>
       </c>
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
@@ -6940,11 +6939,11 @@
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
       <c r="S6" s="12">
-        <f>(F6+O6+R6)/P6</f>
+        <f t="shared" ref="S6:S37" si="4">(F6+O6+R6)/P6</f>
         <v>3.765182186234818</v>
       </c>
       <c r="T6" s="12">
-        <f>(F6+O6)/P6</f>
+        <f t="shared" ref="T6:T37" si="5">(F6+O6)/P6</f>
         <v>3.765182186234818</v>
       </c>
       <c r="U6" s="12">
@@ -7033,11 +7032,11 @@
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
       <c r="S7" s="12">
-        <f>(F7+O7+R7)/P7</f>
+        <f t="shared" si="4"/>
         <v>11.298701298701298</v>
       </c>
       <c r="T7" s="12">
-        <f>(F7+O7)/P7</f>
+        <f t="shared" si="5"/>
         <v>11.298701298701298</v>
       </c>
       <c r="U7" s="12">
@@ -7126,11 +7125,11 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="12">
-        <f>(F8+O8+R8)/P8</f>
+        <f t="shared" si="4"/>
         <v>15.63063063063063</v>
       </c>
       <c r="T8" s="12">
-        <f>(F8+O8)/P8</f>
+        <f t="shared" si="5"/>
         <v>15.63063063063063</v>
       </c>
       <c r="U8" s="12">
@@ -7223,15 +7222,15 @@
         <v>100</v>
       </c>
       <c r="R9" s="4">
-        <f t="shared" ref="R9:R18" si="4">AC9*AD9</f>
+        <f t="shared" ref="R9:R18" si="6">AC9*AD9</f>
         <v>168</v>
       </c>
       <c r="S9" s="16">
-        <f>(F9+O9+R9)/P9</f>
+        <f t="shared" si="4"/>
         <v>168</v>
       </c>
       <c r="T9" s="16">
-        <f>(F9+O9)/P9</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U9" s="16">
@@ -7254,7 +7253,7 @@
       </c>
       <c r="AA9" s="16"/>
       <c r="AB9" s="16">
-        <f>G9*Q9</f>
+        <f t="shared" ref="AB9:AB18" si="7">G9*Q9</f>
         <v>22</v>
       </c>
       <c r="AC9" s="6">
@@ -7262,11 +7261,11 @@
         <v>12</v>
       </c>
       <c r="AD9" s="8">
-        <f>MROUND(Q9, AC9*AF9)/AC9</f>
+        <f t="shared" ref="AD9:AD18" si="8">MROUND(Q9, AC9*AF9)/AC9</f>
         <v>14</v>
       </c>
       <c r="AE9" s="16">
-        <f>AD9*AC9*G9</f>
+        <f t="shared" ref="AE9:AE18" si="9">AD9*AC9*G9</f>
         <v>36.96</v>
       </c>
       <c r="AF9" s="16">
@@ -7278,7 +7277,7 @@
         <v>70</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" ref="AH9:AH18" si="5">AD9/AG9</f>
+        <f t="shared" ref="AH9:AH18" si="10">AD9/AG9</f>
         <v>0.2</v>
       </c>
       <c r="AI9" s="16"/>
@@ -7348,15 +7347,15 @@
         <v>97.199999999999989</v>
       </c>
       <c r="R10" s="4">
+        <f t="shared" si="6"/>
+        <v>168</v>
+      </c>
+      <c r="S10" s="16">
         <f t="shared" si="4"/>
-        <v>168</v>
-      </c>
-      <c r="S10" s="16">
-        <f>(F10+O10+R10)/P10</f>
         <v>21.847826086956523</v>
       </c>
       <c r="T10" s="16">
-        <f>(F10+O10)/P10</f>
+        <f t="shared" si="5"/>
         <v>12.717391304347828</v>
       </c>
       <c r="U10" s="16">
@@ -7379,7 +7378,7 @@
       </c>
       <c r="AA10" s="16"/>
       <c r="AB10" s="16">
-        <f>G10*Q10</f>
+        <f t="shared" si="7"/>
         <v>29.159999999999997</v>
       </c>
       <c r="AC10" s="6">
@@ -7387,11 +7386,11 @@
         <v>12</v>
       </c>
       <c r="AD10" s="8">
-        <f>MROUND(Q10, AC10*AF10)/AC10</f>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="AE10" s="16">
-        <f>AD10*AC10*G10</f>
+        <f t="shared" si="9"/>
         <v>50.4</v>
       </c>
       <c r="AF10" s="16">
@@ -7403,7 +7402,7 @@
         <v>70</v>
       </c>
       <c r="AH10" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="AI10" s="16"/>
@@ -7469,19 +7468,19 @@
         <v>134</v>
       </c>
       <c r="Q11" s="4">
-        <f t="shared" ref="Q11:Q18" si="6">14*P11-O11-F11</f>
+        <f t="shared" ref="Q11:Q18" si="11">14*P11-O11-F11</f>
         <v>849</v>
       </c>
       <c r="R11" s="4">
+        <f t="shared" si="6"/>
+        <v>840</v>
+      </c>
+      <c r="S11" s="16">
         <f t="shared" si="4"/>
-        <v>840</v>
-      </c>
-      <c r="S11" s="16">
-        <f>(F11+O11+R11)/P11</f>
         <v>13.932835820895523</v>
       </c>
       <c r="T11" s="16">
-        <f>(F11+O11)/P11</f>
+        <f t="shared" si="5"/>
         <v>7.6641791044776122</v>
       </c>
       <c r="U11" s="16">
@@ -7504,7 +7503,7 @@
       </c>
       <c r="AA11" s="16"/>
       <c r="AB11" s="16">
-        <f>G11*Q11</f>
+        <f t="shared" si="7"/>
         <v>237.72000000000003</v>
       </c>
       <c r="AC11" s="6">
@@ -7512,11 +7511,11 @@
         <v>6</v>
       </c>
       <c r="AD11" s="8">
-        <f>MROUND(Q11, AC11*AF11)/AC11</f>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="AE11" s="16">
-        <f>AD11*AC11*G11</f>
+        <f t="shared" si="9"/>
         <v>235.20000000000002</v>
       </c>
       <c r="AF11" s="16">
@@ -7528,7 +7527,7 @@
         <v>140</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AI11" s="16"/>
@@ -7594,19 +7593,19 @@
         <v>71.599999999999994</v>
       </c>
       <c r="Q12" s="4">
+        <f t="shared" si="11"/>
+        <v>289.39999999999986</v>
+      </c>
+      <c r="R12" s="4">
         <f t="shared" si="6"/>
-        <v>289.39999999999986</v>
-      </c>
-      <c r="R12" s="4">
+        <v>336</v>
+      </c>
+      <c r="S12" s="16">
         <f t="shared" si="4"/>
-        <v>336</v>
-      </c>
-      <c r="S12" s="16">
-        <f>(F12+O12+R12)/P12</f>
         <v>14.650837988826817</v>
       </c>
       <c r="T12" s="16">
-        <f>(F12+O12)/P12</f>
+        <f t="shared" si="5"/>
         <v>9.9581005586592184</v>
       </c>
       <c r="U12" s="16">
@@ -7629,7 +7628,7 @@
       </c>
       <c r="AA12" s="16"/>
       <c r="AB12" s="16">
-        <f>G12*Q12</f>
+        <f t="shared" si="7"/>
         <v>69.45599999999996</v>
       </c>
       <c r="AC12" s="6">
@@ -7637,11 +7636,11 @@
         <v>12</v>
       </c>
       <c r="AD12" s="8">
-        <f>MROUND(Q12, AC12*AF12)/AC12</f>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="AE12" s="16">
-        <f>AD12*AC12*G12</f>
+        <f t="shared" si="9"/>
         <v>80.64</v>
       </c>
       <c r="AF12" s="16">
@@ -7653,7 +7652,7 @@
         <v>70</v>
       </c>
       <c r="AH12" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="AI12" s="16"/>
@@ -7720,15 +7719,15 @@
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="16">
-        <f>(F13+O13+R13)/P13</f>
         <v>21.881028938906752</v>
       </c>
       <c r="T13" s="16">
-        <f>(F13+O13)/P13</f>
+        <f t="shared" si="5"/>
         <v>21.881028938906752</v>
       </c>
       <c r="U13" s="16">
@@ -7751,7 +7750,7 @@
       </c>
       <c r="AA13" s="16"/>
       <c r="AB13" s="16">
-        <f>G13*Q13</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC13" s="6">
@@ -7759,11 +7758,11 @@
         <v>12</v>
       </c>
       <c r="AD13" s="8">
-        <f>MROUND(Q13, AC13*AF13)/AC13</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE13" s="16">
-        <f>AD13*AC13*G13</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF13" s="16">
@@ -7775,7 +7774,7 @@
         <v>70</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AI13" s="16"/>
@@ -7841,19 +7840,19 @@
         <v>62.8</v>
       </c>
       <c r="Q14" s="4">
+        <f t="shared" si="11"/>
+        <v>185.19999999999993</v>
+      </c>
+      <c r="R14" s="4">
         <f t="shared" si="6"/>
-        <v>185.19999999999993</v>
-      </c>
-      <c r="R14" s="4">
+        <v>168</v>
+      </c>
+      <c r="S14" s="16">
         <f t="shared" si="4"/>
-        <v>168</v>
-      </c>
-      <c r="S14" s="16">
-        <f>(F14+O14+R14)/P14</f>
         <v>13.726114649681529</v>
       </c>
       <c r="T14" s="16">
-        <f>(F14+O14)/P14</f>
+        <f t="shared" si="5"/>
         <v>11.050955414012739</v>
       </c>
       <c r="U14" s="16">
@@ -7876,7 +7875,7 @@
       </c>
       <c r="AA14" s="16"/>
       <c r="AB14" s="16">
-        <f>G14*Q14</f>
+        <f t="shared" si="7"/>
         <v>44.447999999999979</v>
       </c>
       <c r="AC14" s="6">
@@ -7884,11 +7883,11 @@
         <v>12</v>
       </c>
       <c r="AD14" s="8">
-        <f>MROUND(Q14, AC14*AF14)/AC14</f>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="AE14" s="16">
-        <f>AD14*AC14*G14</f>
+        <f t="shared" si="9"/>
         <v>40.32</v>
       </c>
       <c r="AF14" s="16">
@@ -7900,7 +7899,7 @@
         <v>70</v>
       </c>
       <c r="AH14" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="AI14" s="16"/>
@@ -7970,19 +7969,19 @@
         <v>217</v>
       </c>
       <c r="Q15" s="4">
+        <f t="shared" si="11"/>
+        <v>1361</v>
+      </c>
+      <c r="R15" s="4">
         <f t="shared" si="6"/>
-        <v>1361</v>
-      </c>
-      <c r="R15" s="4">
+        <v>1344</v>
+      </c>
+      <c r="S15" s="16">
         <f t="shared" si="4"/>
-        <v>1344</v>
-      </c>
-      <c r="S15" s="16">
-        <f>(F15+O15+R15)/P15</f>
         <v>13.921658986175116</v>
       </c>
       <c r="T15" s="16">
-        <f>(F15+O15)/P15</f>
+        <f t="shared" si="5"/>
         <v>7.7281105990783407</v>
       </c>
       <c r="U15" s="16">
@@ -8005,7 +8004,7 @@
       </c>
       <c r="AA15" s="16"/>
       <c r="AB15" s="16">
-        <f>G15*Q15</f>
+        <f t="shared" si="7"/>
         <v>326.64</v>
       </c>
       <c r="AC15" s="6">
@@ -8013,11 +8012,11 @@
         <v>12</v>
       </c>
       <c r="AD15" s="8">
-        <f>MROUND(Q15, AC15*AF15)/AC15</f>
+        <f t="shared" si="8"/>
         <v>112</v>
       </c>
       <c r="AE15" s="16">
-        <f>AD15*AC15*G15</f>
+        <f t="shared" si="9"/>
         <v>322.56</v>
       </c>
       <c r="AF15" s="16">
@@ -8029,7 +8028,7 @@
         <v>70</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
       <c r="AI15" s="16"/>
@@ -8096,15 +8095,15 @@
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="16">
-        <f>(F16+O16+R16)/P16</f>
         <v>15.049019607843139</v>
       </c>
       <c r="T16" s="16">
-        <f>(F16+O16)/P16</f>
+        <f t="shared" si="5"/>
         <v>15.049019607843139</v>
       </c>
       <c r="U16" s="16">
@@ -8127,7 +8126,7 @@
       </c>
       <c r="AA16" s="16"/>
       <c r="AB16" s="16">
-        <f>G16*Q16</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC16" s="6">
@@ -8135,11 +8134,11 @@
         <v>8</v>
       </c>
       <c r="AD16" s="8">
-        <f>MROUND(Q16, AC16*AF16)/AC16</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE16" s="16">
-        <f>AD16*AC16*G16</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF16" s="16">
@@ -8151,7 +8150,7 @@
         <v>70</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AI16" s="16"/>
@@ -8172,7 +8171,7 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>38</v>
@@ -8217,19 +8216,19 @@
         <v>115.2</v>
       </c>
       <c r="Q17" s="4">
+        <f t="shared" si="11"/>
+        <v>997.8</v>
+      </c>
+      <c r="R17" s="4">
         <f t="shared" si="6"/>
-        <v>997.8</v>
-      </c>
-      <c r="R17" s="4">
+        <v>1008</v>
+      </c>
+      <c r="S17" s="16">
         <f t="shared" si="4"/>
-        <v>1008</v>
-      </c>
-      <c r="S17" s="16">
-        <f>(F17+O17+R17)/P17</f>
         <v>14.088541666666666</v>
       </c>
       <c r="T17" s="16">
-        <f>(F17+O17)/P17</f>
+        <f t="shared" si="5"/>
         <v>5.338541666666667</v>
       </c>
       <c r="U17" s="16">
@@ -8252,7 +8251,7 @@
       </c>
       <c r="AA17" s="16"/>
       <c r="AB17" s="16">
-        <f>G17*Q17</f>
+        <f t="shared" si="7"/>
         <v>89.801999999999992</v>
       </c>
       <c r="AC17" s="6">
@@ -8260,11 +8259,11 @@
         <v>24</v>
       </c>
       <c r="AD17" s="8">
-        <f>MROUND(Q17, AC17*AF17)/AC17</f>
+        <f t="shared" si="8"/>
         <v>42</v>
       </c>
       <c r="AE17" s="16">
-        <f>AD17*AC17*G17</f>
+        <f t="shared" si="9"/>
         <v>90.72</v>
       </c>
       <c r="AF17" s="16">
@@ -8276,7 +8275,7 @@
         <v>126</v>
       </c>
       <c r="AH17" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AI17" s="16"/>
@@ -8297,7 +8296,7 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>38</v>
@@ -8342,19 +8341,19 @@
         <v>92.6</v>
       </c>
       <c r="Q18" s="4">
+        <f t="shared" si="11"/>
+        <v>388.39999999999986</v>
+      </c>
+      <c r="R18" s="4">
         <f t="shared" si="6"/>
-        <v>388.39999999999986</v>
-      </c>
-      <c r="R18" s="4">
+        <v>420</v>
+      </c>
+      <c r="S18" s="16">
         <f t="shared" si="4"/>
-        <v>420</v>
-      </c>
-      <c r="S18" s="16">
-        <f>(F18+O18+R18)/P18</f>
         <v>14.341252699784018</v>
       </c>
       <c r="T18" s="16">
-        <f>(F18+O18)/P18</f>
+        <f t="shared" si="5"/>
         <v>9.8056155507559399</v>
       </c>
       <c r="U18" s="16">
@@ -8377,7 +8376,7 @@
       </c>
       <c r="AA18" s="16"/>
       <c r="AB18" s="16">
-        <f>G18*Q18</f>
+        <f t="shared" si="7"/>
         <v>139.82399999999996</v>
       </c>
       <c r="AC18" s="6">
@@ -8385,11 +8384,11 @@
         <v>10</v>
       </c>
       <c r="AD18" s="8">
-        <f>MROUND(Q18, AC18*AF18)/AC18</f>
+        <f t="shared" si="8"/>
         <v>42</v>
       </c>
       <c r="AE18" s="16">
-        <f>AD18*AC18*G18</f>
+        <f t="shared" si="9"/>
         <v>151.19999999999999</v>
       </c>
       <c r="AF18" s="16">
@@ -8401,7 +8400,7 @@
         <v>70</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
       <c r="AI18" s="16"/>
@@ -8422,7 +8421,7 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>38</v>
@@ -8432,7 +8431,7 @@
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
-      <c r="F19" s="17">
+      <c r="F19" s="12">
         <v>831</v>
       </c>
       <c r="G19" s="13">
@@ -8440,10 +8439,10 @@
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="K19" s="12"/>
       <c r="L19" s="12">
@@ -8460,11 +8459,11 @@
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
       <c r="S19" s="12" t="e">
-        <f>(F19+O19+R19)/P19</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T19" s="12" t="e">
-        <f>(F19+O19)/P19</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U19" s="12">
@@ -8485,7 +8484,9 @@
       <c r="Z19" s="12">
         <v>0</v>
       </c>
-      <c r="AA19" s="12"/>
+      <c r="AA19" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="AB19" s="12"/>
       <c r="AC19" s="13"/>
       <c r="AD19" s="15"/>
@@ -8511,7 +8512,7 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>38</v>
@@ -8523,9 +8524,9 @@
       <c r="E20" s="16">
         <v>284</v>
       </c>
-      <c r="F20" s="17">
-        <f>252+F19</f>
-        <v>1083</v>
+      <c r="F20" s="16">
+        <f>252</f>
+        <v>252</v>
       </c>
       <c r="G20" s="6">
         <f>VLOOKUP(A20,[1]Sheet!$A:$I,7,0)</f>
@@ -8556,18 +8557,21 @@
         <f t="shared" si="3"/>
         <v>56.8</v>
       </c>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="4">
+        <f t="shared" ref="Q20:Q40" si="12">14*P20-O20-F20</f>
+        <v>543.19999999999993</v>
+      </c>
       <c r="R20" s="4">
-        <f t="shared" ref="R20:R42" si="7">AC20*AD20</f>
-        <v>0</v>
+        <f t="shared" ref="R20:R42" si="13">AC20*AD20</f>
+        <v>504</v>
       </c>
       <c r="S20" s="16">
-        <f>(F20+O20+R20)/P20</f>
-        <v>19.066901408450704</v>
+        <f t="shared" si="4"/>
+        <v>13.309859154929578</v>
       </c>
       <c r="T20" s="16">
-        <f>(F20+O20)/P20</f>
-        <v>19.066901408450704</v>
+        <f t="shared" si="5"/>
+        <v>4.436619718309859</v>
       </c>
       <c r="U20" s="16">
         <v>38.4</v>
@@ -8587,24 +8591,22 @@
       <c r="Z20" s="16">
         <v>42</v>
       </c>
-      <c r="AA20" s="18" t="s">
-        <v>52</v>
-      </c>
+      <c r="AA20" s="16"/>
       <c r="AB20" s="16">
-        <f>G20*Q20</f>
-        <v>0</v>
+        <f t="shared" ref="AB20:AB42" si="14">G20*Q20</f>
+        <v>108.63999999999999</v>
       </c>
       <c r="AC20" s="6">
         <f>VLOOKUP(A20,[1]Sheet!$A:$AJ,32,0)</f>
         <v>12</v>
       </c>
       <c r="AD20" s="8">
-        <f>MROUND(Q20, AC20*AF20)/AC20</f>
-        <v>0</v>
+        <f t="shared" ref="AD20:AD42" si="15">MROUND(Q20, AC20*AF20)/AC20</f>
+        <v>42</v>
       </c>
       <c r="AE20" s="16">
-        <f>AD20*AC20*G20</f>
-        <v>0</v>
+        <f t="shared" ref="AE20:AE42" si="16">AD20*AC20*G20</f>
+        <v>100.80000000000001</v>
       </c>
       <c r="AF20" s="16">
         <f>VLOOKUP(A20,[1]Sheet!$A:$AJ,35,0)</f>
@@ -8615,8 +8617,8 @@
         <v>70</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" ref="AH20:AH42" si="8">AD20/AG20</f>
-        <v>0</v>
+        <f t="shared" ref="AH20:AH42" si="17">AD20/AG20</f>
+        <v>0.6</v>
       </c>
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
@@ -8636,7 +8638,7 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>38</v>
@@ -8681,19 +8683,19 @@
         <v>81.8</v>
       </c>
       <c r="Q21" s="4">
-        <f t="shared" ref="Q21:Q40" si="9">14*P21-O21-F21</f>
+        <f t="shared" si="12"/>
         <v>349.20000000000005</v>
       </c>
       <c r="R21" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>336</v>
       </c>
       <c r="S21" s="16">
-        <f>(F21+O21+R21)/P21</f>
+        <f t="shared" si="4"/>
         <v>13.838630806845966</v>
       </c>
       <c r="T21" s="16">
-        <f>(F21+O21)/P21</f>
+        <f t="shared" si="5"/>
         <v>9.7310513447432765</v>
       </c>
       <c r="U21" s="16">
@@ -8716,7 +8718,7 @@
       </c>
       <c r="AA21" s="16"/>
       <c r="AB21" s="16">
-        <f>G21*Q21</f>
+        <f t="shared" si="14"/>
         <v>69.840000000000018</v>
       </c>
       <c r="AC21" s="6">
@@ -8724,11 +8726,11 @@
         <v>12</v>
       </c>
       <c r="AD21" s="8">
-        <f>MROUND(Q21, AC21*AF21)/AC21</f>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
       <c r="AE21" s="16">
-        <f>AD21*AC21*G21</f>
+        <f t="shared" si="16"/>
         <v>67.2</v>
       </c>
       <c r="AF21" s="16">
@@ -8740,7 +8742,7 @@
         <v>70</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
       <c r="AI21" s="16"/>
@@ -8761,10 +8763,10 @@
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>61</v>
       </c>
       <c r="C22" s="16">
         <v>155</v>
@@ -8810,15 +8812,15 @@
         <v>380.31999999999988</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>360</v>
       </c>
       <c r="S22" s="16">
-        <f>(F22+O22+R22)/P22</f>
+        <f t="shared" si="4"/>
         <v>12.488676396577757</v>
       </c>
       <c r="T22" s="16">
-        <f>(F22+O22)/P22</f>
+        <f t="shared" si="5"/>
         <v>3.4297936587820841</v>
       </c>
       <c r="U22" s="16">
@@ -8841,7 +8843,7 @@
       </c>
       <c r="AA22" s="16"/>
       <c r="AB22" s="16">
-        <f>G22*Q22</f>
+        <f t="shared" si="14"/>
         <v>380.31999999999988</v>
       </c>
       <c r="AC22" s="6">
@@ -8849,11 +8851,11 @@
         <v>5</v>
       </c>
       <c r="AD22" s="8">
-        <f>MROUND(Q22, AC22*AF22)/AC22</f>
+        <f t="shared" si="15"/>
         <v>72</v>
       </c>
       <c r="AE22" s="16">
-        <f>AD22*AC22*G22</f>
+        <f t="shared" si="16"/>
         <v>360</v>
       </c>
       <c r="AF22" s="16">
@@ -8865,7 +8867,7 @@
         <v>84</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="AI22" s="16"/>
@@ -8886,10 +8888,10 @@
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="16">
         <v>286.5</v>
@@ -8901,14 +8903,14 @@
       <c r="F23" s="16">
         <v>144</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="19">
         <v>1</v>
       </c>
       <c r="H23" s="16">
         <v>180</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J23" s="16"/>
       <c r="K23" s="16">
@@ -8928,19 +8930,19 @@
         <v>28.5</v>
       </c>
       <c r="Q23" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>57</v>
       </c>
       <c r="R23" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>66</v>
       </c>
       <c r="S23" s="16">
-        <f>(F23+O23+R23)/P23</f>
+        <f t="shared" si="4"/>
         <v>14.315789473684211</v>
       </c>
       <c r="T23" s="16">
-        <f>(F23+O23)/P23</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="U23" s="16">
@@ -8963,18 +8965,18 @@
       </c>
       <c r="AA23" s="16"/>
       <c r="AB23" s="16">
-        <f>G23*Q23</f>
+        <f t="shared" si="14"/>
         <v>57</v>
       </c>
       <c r="AC23" s="6">
         <v>5.5</v>
       </c>
       <c r="AD23" s="8">
-        <f>MROUND(Q23, AC23*AF23)/AC23</f>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="AE23" s="16">
-        <f>AD23*AC23*G23</f>
+        <f t="shared" si="16"/>
         <v>66</v>
       </c>
       <c r="AF23" s="16">
@@ -8984,7 +8986,7 @@
         <v>84</v>
       </c>
       <c r="AH23" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI23" s="16"/>
@@ -9005,10 +9007,10 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="16">
         <v>267</v>
@@ -9053,15 +9055,15 @@
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S24" s="16">
-        <f>(F24+O24+R24)/P24</f>
+        <f t="shared" si="4"/>
         <v>14.056603773584905</v>
       </c>
       <c r="T24" s="16">
-        <f>(F24+O24)/P24</f>
+        <f t="shared" si="5"/>
         <v>14.056603773584905</v>
       </c>
       <c r="U24" s="16">
@@ -9084,7 +9086,7 @@
       </c>
       <c r="AA24" s="16"/>
       <c r="AB24" s="16">
-        <f>G24*Q24</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC24" s="6">
@@ -9092,11 +9094,11 @@
         <v>3</v>
       </c>
       <c r="AD24" s="8">
-        <f>MROUND(Q24, AC24*AF24)/AC24</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE24" s="16">
-        <f>AD24*AC24*G24</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF24" s="16">
@@ -9108,7 +9110,7 @@
         <v>126</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI24" s="16"/>
@@ -9129,7 +9131,7 @@
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>38</v>
@@ -9172,19 +9174,19 @@
         <v>36.6</v>
       </c>
       <c r="Q25" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>92.399999999999977</v>
       </c>
       <c r="R25" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="S25" s="16">
-        <f>(F25+O25+R25)/P25</f>
+        <f t="shared" si="4"/>
         <v>13.770491803278688</v>
       </c>
       <c r="T25" s="16">
-        <f>(F25+O25)/P25</f>
+        <f t="shared" si="5"/>
         <v>11.475409836065573</v>
       </c>
       <c r="U25" s="16">
@@ -9207,7 +9209,7 @@
       </c>
       <c r="AA25" s="16"/>
       <c r="AB25" s="16">
-        <f>G25*Q25</f>
+        <f t="shared" si="14"/>
         <v>23.099999999999994</v>
       </c>
       <c r="AC25" s="6">
@@ -9215,11 +9217,11 @@
         <v>6</v>
       </c>
       <c r="AD25" s="8">
-        <f>MROUND(Q25, AC25*AF25)/AC25</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="AE25" s="16">
-        <f>AD25*AC25*G25</f>
+        <f t="shared" si="16"/>
         <v>21</v>
       </c>
       <c r="AF25" s="16">
@@ -9231,7 +9233,7 @@
         <v>140</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.1</v>
       </c>
       <c r="AI25" s="16"/>
@@ -9252,7 +9254,7 @@
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>38</v>
@@ -9298,15 +9300,15 @@
       </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S26" s="16">
-        <f>(F26+O26+R26)/P26</f>
+        <f t="shared" si="4"/>
         <v>15.350553505535055</v>
       </c>
       <c r="T26" s="16">
-        <f>(F26+O26)/P26</f>
+        <f t="shared" si="5"/>
         <v>15.350553505535055</v>
       </c>
       <c r="U26" s="16">
@@ -9329,7 +9331,7 @@
       </c>
       <c r="AA26" s="16"/>
       <c r="AB26" s="16">
-        <f>G26*Q26</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC26" s="6">
@@ -9337,11 +9339,11 @@
         <v>6</v>
       </c>
       <c r="AD26" s="8">
-        <f>MROUND(Q26, AC26*AF26)/AC26</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE26" s="16">
-        <f>AD26*AC26*G26</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF26" s="16">
@@ -9353,7 +9355,7 @@
         <v>140</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI26" s="16"/>
@@ -9374,10 +9376,10 @@
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" s="16">
         <v>690</v>
@@ -9419,19 +9421,19 @@
         <v>79</v>
       </c>
       <c r="Q27" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>235</v>
       </c>
       <c r="R27" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>216</v>
       </c>
       <c r="S27" s="16">
-        <f>(F27+O27+R27)/P27</f>
+        <f t="shared" si="4"/>
         <v>13.759493670886076</v>
       </c>
       <c r="T27" s="16">
-        <f>(F27+O27)/P27</f>
+        <f t="shared" si="5"/>
         <v>11.025316455696203</v>
       </c>
       <c r="U27" s="16">
@@ -9454,7 +9456,7 @@
       </c>
       <c r="AA27" s="16"/>
       <c r="AB27" s="16">
-        <f>G27*Q27</f>
+        <f t="shared" si="14"/>
         <v>235</v>
       </c>
       <c r="AC27" s="6">
@@ -9462,11 +9464,11 @@
         <v>6</v>
       </c>
       <c r="AD27" s="8">
-        <f>MROUND(Q27, AC27*AF27)/AC27</f>
+        <f t="shared" si="15"/>
         <v>36</v>
       </c>
       <c r="AE27" s="16">
-        <f>AD27*AC27*G27</f>
+        <f t="shared" si="16"/>
         <v>216</v>
       </c>
       <c r="AF27" s="16">
@@ -9478,7 +9480,7 @@
         <v>84</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AI27" s="16"/>
@@ -9499,7 +9501,7 @@
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>38</v>
@@ -9547,15 +9549,15 @@
       </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S28" s="16">
-        <f>(F28+O28+R28)/P28</f>
+        <f t="shared" si="4"/>
         <v>20.350877192982455</v>
       </c>
       <c r="T28" s="16">
-        <f>(F28+O28)/P28</f>
+        <f t="shared" si="5"/>
         <v>20.350877192982455</v>
       </c>
       <c r="U28" s="16">
@@ -9578,7 +9580,7 @@
       </c>
       <c r="AA28" s="16"/>
       <c r="AB28" s="16">
-        <f>G28*Q28</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC28" s="6">
@@ -9586,11 +9588,11 @@
         <v>12</v>
       </c>
       <c r="AD28" s="8">
-        <f>MROUND(Q28, AC28*AF28)/AC28</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE28" s="16">
-        <f>AD28*AC28*G28</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF28" s="16">
@@ -9602,7 +9604,7 @@
         <v>70</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI28" s="16"/>
@@ -9623,7 +9625,7 @@
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>38</v>
@@ -9668,19 +9670,19 @@
         <v>101.8</v>
       </c>
       <c r="Q29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>509.20000000000005</v>
       </c>
       <c r="R29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>504</v>
       </c>
       <c r="S29" s="16">
-        <f>(F29+O29+R29)/P29</f>
+        <f t="shared" si="4"/>
         <v>13.948919449901769</v>
       </c>
       <c r="T29" s="16">
-        <f>(F29+O29)/P29</f>
+        <f t="shared" si="5"/>
         <v>8.9980353634577614</v>
       </c>
       <c r="U29" s="16">
@@ -9703,7 +9705,7 @@
       </c>
       <c r="AA29" s="16"/>
       <c r="AB29" s="16">
-        <f>G29*Q29</f>
+        <f t="shared" si="14"/>
         <v>127.30000000000001</v>
       </c>
       <c r="AC29" s="6">
@@ -9711,11 +9713,11 @@
         <v>12</v>
       </c>
       <c r="AD29" s="8">
-        <f>MROUND(Q29, AC29*AF29)/AC29</f>
+        <f t="shared" si="15"/>
         <v>42</v>
       </c>
       <c r="AE29" s="16">
-        <f>AD29*AC29*G29</f>
+        <f t="shared" si="16"/>
         <v>126</v>
       </c>
       <c r="AF29" s="16">
@@ -9727,7 +9729,7 @@
         <v>70</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.6</v>
       </c>
       <c r="AI29" s="16"/>
@@ -9748,7 +9750,7 @@
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>38</v>
@@ -9797,15 +9799,15 @@
         <v>139</v>
       </c>
       <c r="R30" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>168</v>
       </c>
       <c r="S30" s="16">
-        <f>(F30+O30+R30)/P30</f>
+        <f t="shared" si="4"/>
         <v>15.383597883597885</v>
       </c>
       <c r="T30" s="16">
-        <f>(F30+O30)/P30</f>
+        <f t="shared" si="5"/>
         <v>13.161375661375663</v>
       </c>
       <c r="U30" s="16">
@@ -9828,7 +9830,7 @@
       </c>
       <c r="AA30" s="16"/>
       <c r="AB30" s="16">
-        <f>G30*Q30</f>
+        <f t="shared" si="14"/>
         <v>34.75</v>
       </c>
       <c r="AC30" s="6">
@@ -9836,11 +9838,11 @@
         <v>12</v>
       </c>
       <c r="AD30" s="8">
-        <f>MROUND(Q30, AC30*AF30)/AC30</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="AE30" s="16">
-        <f>AD30*AC30*G30</f>
+        <f t="shared" si="16"/>
         <v>42</v>
       </c>
       <c r="AF30" s="16">
@@ -9852,7 +9854,7 @@
         <v>70</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AI30" s="16"/>
@@ -9873,7 +9875,7 @@
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>38</v>
@@ -9924,15 +9926,15 @@
         <v>702.59999999999991</v>
       </c>
       <c r="R31" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>672</v>
       </c>
       <c r="S31" s="16">
-        <f>(F31+O31+R31)/P31</f>
+        <f t="shared" si="4"/>
         <v>10.572625698324023</v>
       </c>
       <c r="T31" s="16">
-        <f>(F31+O31)/P31</f>
+        <f t="shared" si="5"/>
         <v>1.1871508379888269</v>
       </c>
       <c r="U31" s="16">
@@ -9955,7 +9957,7 @@
       </c>
       <c r="AA31" s="16"/>
       <c r="AB31" s="16">
-        <f>G31*Q31</f>
+        <f t="shared" si="14"/>
         <v>175.64999999999998</v>
       </c>
       <c r="AC31" s="6">
@@ -9963,11 +9965,11 @@
         <v>12</v>
       </c>
       <c r="AD31" s="8">
-        <f>MROUND(Q31, AC31*AF31)/AC31</f>
+        <f t="shared" si="15"/>
         <v>56</v>
       </c>
       <c r="AE31" s="16">
-        <f>AD31*AC31*G31</f>
+        <f t="shared" si="16"/>
         <v>168</v>
       </c>
       <c r="AF31" s="16">
@@ -9979,7 +9981,7 @@
         <v>70</v>
       </c>
       <c r="AH31" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
       <c r="AI31" s="16"/>
@@ -10000,7 +10002,7 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>38</v>
@@ -10046,15 +10048,15 @@
       </c>
       <c r="Q32" s="4"/>
       <c r="R32" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S32" s="16">
-        <f>(F32+O32+R32)/P32</f>
+        <f t="shared" si="4"/>
         <v>57.307692307692307</v>
       </c>
       <c r="T32" s="16">
-        <f>(F32+O32)/P32</f>
+        <f t="shared" si="5"/>
         <v>57.307692307692307</v>
       </c>
       <c r="U32" s="16">
@@ -10077,7 +10079,7 @@
       </c>
       <c r="AA32" s="16"/>
       <c r="AB32" s="16">
-        <f>G32*Q32</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC32" s="6">
@@ -10085,11 +10087,11 @@
         <v>12</v>
       </c>
       <c r="AD32" s="8">
-        <f>MROUND(Q32, AC32*AF32)/AC32</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE32" s="16">
-        <f>AD32*AC32*G32</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF32" s="16">
@@ -10101,7 +10103,7 @@
         <v>70</v>
       </c>
       <c r="AH32" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI32" s="16"/>
@@ -10122,7 +10124,7 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>38</v>
@@ -10167,19 +10169,19 @@
         <v>36.4</v>
       </c>
       <c r="Q33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>245.59999999999997</v>
       </c>
       <c r="R33" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>288</v>
       </c>
       <c r="S33" s="16">
-        <f>(F33+O33+R33)/P33</f>
+        <f t="shared" si="4"/>
         <v>15.164835164835166</v>
       </c>
       <c r="T33" s="16">
-        <f>(F33+O33)/P33</f>
+        <f t="shared" si="5"/>
         <v>7.2527472527472527</v>
       </c>
       <c r="U33" s="16">
@@ -10202,7 +10204,7 @@
       </c>
       <c r="AA33" s="16"/>
       <c r="AB33" s="16">
-        <f>G33*Q33</f>
+        <f t="shared" si="14"/>
         <v>171.91999999999996</v>
       </c>
       <c r="AC33" s="6">
@@ -10210,11 +10212,11 @@
         <v>8</v>
       </c>
       <c r="AD33" s="8">
-        <f>MROUND(Q33, AC33*AF33)/AC33</f>
+        <f t="shared" si="15"/>
         <v>36</v>
       </c>
       <c r="AE33" s="16">
-        <f>AD33*AC33*G33</f>
+        <f t="shared" si="16"/>
         <v>201.6</v>
       </c>
       <c r="AF33" s="16">
@@ -10226,7 +10228,7 @@
         <v>84</v>
       </c>
       <c r="AH33" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AI33" s="16"/>
@@ -10247,7 +10249,7 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>38</v>
@@ -10296,15 +10298,15 @@
         <v>69</v>
       </c>
       <c r="R34" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>96</v>
       </c>
       <c r="S34" s="16">
-        <f>(F34+O34+R34)/P34</f>
+        <f t="shared" si="4"/>
         <v>16.14406779661017</v>
       </c>
       <c r="T34" s="16">
-        <f>(F34+O34)/P34</f>
+        <f t="shared" si="5"/>
         <v>12.076271186440676</v>
       </c>
       <c r="U34" s="16">
@@ -10327,7 +10329,7 @@
       </c>
       <c r="AA34" s="16"/>
       <c r="AB34" s="16">
-        <f>G34*Q34</f>
+        <f t="shared" si="14"/>
         <v>48.3</v>
       </c>
       <c r="AC34" s="6">
@@ -10335,11 +10337,11 @@
         <v>8</v>
       </c>
       <c r="AD34" s="8">
-        <f>MROUND(Q34, AC34*AF34)/AC34</f>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="AE34" s="16">
-        <f>AD34*AC34*G34</f>
+        <f t="shared" si="16"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AF34" s="16">
@@ -10351,7 +10353,7 @@
         <v>84</v>
       </c>
       <c r="AH34" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI34" s="16"/>
@@ -10372,7 +10374,7 @@
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>38</v>
@@ -10418,15 +10420,15 @@
       </c>
       <c r="Q35" s="4"/>
       <c r="R35" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S35" s="16">
-        <f>(F35+O35+R35)/P35</f>
+        <f t="shared" si="4"/>
         <v>20.517241379310345</v>
       </c>
       <c r="T35" s="16">
-        <f>(F35+O35)/P35</f>
+        <f t="shared" si="5"/>
         <v>20.517241379310345</v>
       </c>
       <c r="U35" s="16">
@@ -10449,7 +10451,7 @@
       </c>
       <c r="AA35" s="16"/>
       <c r="AB35" s="16">
-        <f>G35*Q35</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC35" s="6">
@@ -10457,11 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AD35" s="8">
-        <f>MROUND(Q35, AC35*AF35)/AC35</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE35" s="16">
-        <f>AD35*AC35*G35</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF35" s="16">
@@ -10473,7 +10475,7 @@
         <v>84</v>
       </c>
       <c r="AH35" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI35" s="16"/>
@@ -10494,7 +10496,7 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>38</v>
@@ -10542,15 +10544,15 @@
       </c>
       <c r="Q36" s="4"/>
       <c r="R36" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S36" s="16">
-        <f>(F36+O36+R36)/P36</f>
+        <f t="shared" si="4"/>
         <v>31.5625</v>
       </c>
       <c r="T36" s="16">
-        <f>(F36+O36)/P36</f>
+        <f t="shared" si="5"/>
         <v>31.5625</v>
       </c>
       <c r="U36" s="16">
@@ -10571,11 +10573,11 @@
       <c r="Z36" s="16">
         <v>33.6</v>
       </c>
-      <c r="AA36" s="19" t="s">
-        <v>58</v>
+      <c r="AA36" s="18" t="s">
+        <v>57</v>
       </c>
       <c r="AB36" s="16">
-        <f>G36*Q36</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC36" s="6">
@@ -10583,11 +10585,11 @@
         <v>10</v>
       </c>
       <c r="AD36" s="8">
-        <f>MROUND(Q36, AC36*AF36)/AC36</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE36" s="16">
-        <f>AD36*AC36*G36</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF36" s="16">
@@ -10599,7 +10601,7 @@
         <v>84</v>
       </c>
       <c r="AH36" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI36" s="16"/>
@@ -10620,7 +10622,7 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>38</v>
@@ -10671,15 +10673,15 @@
         <v>63.599999999999994</v>
       </c>
       <c r="R37" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
       <c r="S37" s="16">
-        <f>(F37+O37+R37)/P37</f>
+        <f t="shared" si="4"/>
         <v>19.863013698630137</v>
       </c>
       <c r="T37" s="16">
-        <f>(F37+O37)/P37</f>
+        <f t="shared" si="5"/>
         <v>11.643835616438356</v>
       </c>
       <c r="U37" s="16">
@@ -10702,7 +10704,7 @@
       </c>
       <c r="AA37" s="16"/>
       <c r="AB37" s="16">
-        <f>G37*Q37</f>
+        <f t="shared" si="14"/>
         <v>44.519999999999996</v>
       </c>
       <c r="AC37" s="6">
@@ -10710,11 +10712,11 @@
         <v>10</v>
       </c>
       <c r="AD37" s="8">
-        <f>MROUND(Q37, AC37*AF37)/AC37</f>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="AE37" s="16">
-        <f>AD37*AC37*G37</f>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AF37" s="16">
@@ -10726,7 +10728,7 @@
         <v>84</v>
       </c>
       <c r="AH37" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI37" s="16"/>
@@ -10747,7 +10749,7 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>38</v>
@@ -10781,7 +10783,7 @@
         <v>198</v>
       </c>
       <c r="L38" s="16">
-        <f t="shared" ref="L38:L67" si="10">E38-K38</f>
+        <f t="shared" ref="L38:L67" si="18">E38-K38</f>
         <v>-8</v>
       </c>
       <c r="M38" s="16"/>
@@ -10790,23 +10792,23 @@
         <v>360</v>
       </c>
       <c r="P38" s="16">
-        <f t="shared" ref="P38:P67" si="11">E38/5</f>
+        <f t="shared" ref="P38:P67" si="19">E38/5</f>
         <v>38</v>
       </c>
       <c r="Q38" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>145</v>
       </c>
       <c r="R38" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
       <c r="S38" s="16">
-        <f>(F38+O38+R38)/P38</f>
+        <f t="shared" ref="S38:S69" si="20">(F38+O38+R38)/P38</f>
         <v>13.342105263157896</v>
       </c>
       <c r="T38" s="16">
-        <f>(F38+O38)/P38</f>
+        <f t="shared" ref="T38:T67" si="21">(F38+O38)/P38</f>
         <v>10.184210526315789</v>
       </c>
       <c r="U38" s="16">
@@ -10829,7 +10831,7 @@
       </c>
       <c r="AA38" s="16"/>
       <c r="AB38" s="16">
-        <f>G38*Q38</f>
+        <f t="shared" si="14"/>
         <v>101.5</v>
       </c>
       <c r="AC38" s="6">
@@ -10837,11 +10839,11 @@
         <v>10</v>
       </c>
       <c r="AD38" s="8">
-        <f>MROUND(Q38, AC38*AF38)/AC38</f>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="AE38" s="16">
-        <f>AD38*AC38*G38</f>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AF38" s="16">
@@ -10853,7 +10855,7 @@
         <v>84</v>
       </c>
       <c r="AH38" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI38" s="16"/>
@@ -10874,7 +10876,7 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>38</v>
@@ -10906,7 +10908,7 @@
         <v>75</v>
       </c>
       <c r="L39" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M39" s="16"/>
@@ -10915,7 +10917,7 @@
         <v>120</v>
       </c>
       <c r="P39" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>15</v>
       </c>
       <c r="Q39" s="4">
@@ -10923,15 +10925,15 @@
         <v>62</v>
       </c>
       <c r="R39" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
       <c r="S39" s="16">
-        <f>(F39+O39+R39)/P39</f>
+        <f t="shared" si="20"/>
         <v>19.866666666666667</v>
       </c>
       <c r="T39" s="16">
-        <f>(F39+O39)/P39</f>
+        <f t="shared" si="21"/>
         <v>11.866666666666667</v>
       </c>
       <c r="U39" s="16">
@@ -10954,7 +10956,7 @@
       </c>
       <c r="AA39" s="16"/>
       <c r="AB39" s="16">
-        <f>G39*Q39</f>
+        <f t="shared" si="14"/>
         <v>43.4</v>
       </c>
       <c r="AC39" s="6">
@@ -10962,11 +10964,11 @@
         <v>10</v>
       </c>
       <c r="AD39" s="8">
-        <f>MROUND(Q39, AC39*AF39)/AC39</f>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="AE39" s="16">
-        <f>AD39*AC39*G39</f>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AF39" s="16">
@@ -10978,7 +10980,7 @@
         <v>84</v>
       </c>
       <c r="AH39" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI39" s="16"/>
@@ -10999,10 +11001,10 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C40" s="16">
         <v>720</v>
@@ -11033,7 +11035,7 @@
         <v>466.4</v>
       </c>
       <c r="L40" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-6.3999999999999773</v>
       </c>
       <c r="M40" s="16"/>
@@ -11042,23 +11044,23 @@
         <v>360</v>
       </c>
       <c r="P40" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>92</v>
       </c>
       <c r="Q40" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>668</v>
       </c>
       <c r="R40" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>660</v>
       </c>
       <c r="S40" s="16">
-        <f>(F40+O40+R40)/P40</f>
+        <f t="shared" si="20"/>
         <v>13.913043478260869</v>
       </c>
       <c r="T40" s="16">
-        <f>(F40+O40)/P40</f>
+        <f t="shared" si="21"/>
         <v>6.7391304347826084</v>
       </c>
       <c r="U40" s="16">
@@ -11081,7 +11083,7 @@
       </c>
       <c r="AA40" s="16"/>
       <c r="AB40" s="16">
-        <f>G40*Q40</f>
+        <f t="shared" si="14"/>
         <v>668</v>
       </c>
       <c r="AC40" s="6">
@@ -11089,11 +11091,11 @@
         <v>5</v>
       </c>
       <c r="AD40" s="8">
-        <f>MROUND(Q40, AC40*AF40)/AC40</f>
+        <f t="shared" si="15"/>
         <v>132</v>
       </c>
       <c r="AE40" s="16">
-        <f>AD40*AC40*G40</f>
+        <f t="shared" si="16"/>
         <v>660</v>
       </c>
       <c r="AF40" s="16">
@@ -11105,7 +11107,7 @@
         <v>144</v>
       </c>
       <c r="AH40" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="AI40" s="16"/>
@@ -11126,7 +11128,7 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>38</v>
@@ -11158,7 +11160,7 @@
         <v>186</v>
       </c>
       <c r="L41" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-25</v>
       </c>
       <c r="M41" s="16"/>
@@ -11167,20 +11169,20 @@
         <v>384</v>
       </c>
       <c r="P41" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>32.200000000000003</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S41" s="16">
-        <f>(F41+O41+R41)/P41</f>
+        <f t="shared" si="20"/>
         <v>15.93167701863354</v>
       </c>
       <c r="T41" s="16">
-        <f>(F41+O41)/P41</f>
+        <f t="shared" si="21"/>
         <v>15.93167701863354</v>
       </c>
       <c r="U41" s="16">
@@ -11203,7 +11205,7 @@
       </c>
       <c r="AA41" s="16"/>
       <c r="AB41" s="16">
-        <f>G41*Q41</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC41" s="6">
@@ -11211,11 +11213,11 @@
         <v>16</v>
       </c>
       <c r="AD41" s="8">
-        <f>MROUND(Q41, AC41*AF41)/AC41</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE41" s="16">
-        <f>AD41*AC41*G41</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF41" s="16">
@@ -11227,7 +11229,7 @@
         <v>84</v>
       </c>
       <c r="AH41" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI41" s="16"/>
@@ -11248,7 +11250,7 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>38</v>
@@ -11282,7 +11284,7 @@
         <v>266</v>
       </c>
       <c r="L42" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M42" s="16"/>
@@ -11291,7 +11293,7 @@
         <v>480</v>
       </c>
       <c r="P42" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>53.2</v>
       </c>
       <c r="Q42" s="4">
@@ -11299,15 +11301,15 @@
         <v>95</v>
       </c>
       <c r="R42" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
       <c r="S42" s="16">
-        <f>(F42+O42+R42)/P42</f>
+        <f t="shared" si="20"/>
         <v>15.469924812030074</v>
       </c>
       <c r="T42" s="16">
-        <f>(F42+O42)/P42</f>
+        <f t="shared" si="21"/>
         <v>13.214285714285714</v>
       </c>
       <c r="U42" s="16">
@@ -11330,7 +11332,7 @@
       </c>
       <c r="AA42" s="16"/>
       <c r="AB42" s="16">
-        <f>G42*Q42</f>
+        <f t="shared" si="14"/>
         <v>66.5</v>
       </c>
       <c r="AC42" s="6">
@@ -11338,11 +11340,11 @@
         <v>10</v>
       </c>
       <c r="AD42" s="8">
-        <f>MROUND(Q42, AC42*AF42)/AC42</f>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="AE42" s="16">
-        <f>AD42*AC42*G42</f>
+        <f t="shared" si="16"/>
         <v>84</v>
       </c>
       <c r="AF42" s="16">
@@ -11354,7 +11356,7 @@
         <v>84</v>
       </c>
       <c r="AH42" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI42" s="16"/>
@@ -11375,7 +11377,7 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>38</v>
@@ -11393,33 +11395,33 @@
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K43" s="12">
         <v>1</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
       <c r="O43" s="12"/>
       <c r="P43" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>0.2</v>
       </c>
       <c r="Q43" s="14"/>
       <c r="R43" s="14"/>
       <c r="S43" s="12">
-        <f>(F43+O43+R43)/P43</f>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="T43" s="12">
-        <f>(F43+O43)/P43</f>
+        <f t="shared" si="21"/>
         <v>-10</v>
       </c>
       <c r="U43" s="12">
@@ -11466,7 +11468,7 @@
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>38</v>
@@ -11500,7 +11502,7 @@
         <v>215</v>
       </c>
       <c r="L44" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-23</v>
       </c>
       <c r="M44" s="16"/>
@@ -11509,23 +11511,23 @@
         <v>192</v>
       </c>
       <c r="P44" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>38.4</v>
       </c>
       <c r="Q44" s="4">
-        <f t="shared" ref="Q44:Q66" si="12">14*P44-O44-F44</f>
+        <f t="shared" ref="Q44:Q66" si="22">14*P44-O44-F44</f>
         <v>217.60000000000002</v>
       </c>
       <c r="R44" s="4">
-        <f t="shared" ref="R44:R66" si="13">AC44*AD44</f>
+        <f t="shared" ref="R44:R66" si="23">AC44*AD44</f>
         <v>192</v>
       </c>
       <c r="S44" s="16">
-        <f>(F44+O44+R44)/P44</f>
+        <f t="shared" si="20"/>
         <v>13.333333333333334</v>
       </c>
       <c r="T44" s="16">
-        <f>(F44+O44)/P44</f>
+        <f t="shared" si="21"/>
         <v>8.3333333333333339</v>
       </c>
       <c r="U44" s="16">
@@ -11548,7 +11550,7 @@
       </c>
       <c r="AA44" s="16"/>
       <c r="AB44" s="16">
-        <f>G44*Q44</f>
+        <f t="shared" ref="AB44:AB66" si="24">G44*Q44</f>
         <v>87.04000000000002</v>
       </c>
       <c r="AC44" s="6">
@@ -11556,11 +11558,11 @@
         <v>16</v>
       </c>
       <c r="AD44" s="8">
-        <f>MROUND(Q44, AC44*AF44)/AC44</f>
+        <f t="shared" ref="AD44:AD66" si="25">MROUND(Q44, AC44*AF44)/AC44</f>
         <v>12</v>
       </c>
       <c r="AE44" s="16">
-        <f>AD44*AC44*G44</f>
+        <f t="shared" ref="AE44:AE66" si="26">AD44*AC44*G44</f>
         <v>76.800000000000011</v>
       </c>
       <c r="AF44" s="16">
@@ -11572,7 +11574,7 @@
         <v>84</v>
       </c>
       <c r="AH44" s="8">
-        <f t="shared" ref="AH44:AH66" si="14">AD44/AG44</f>
+        <f t="shared" ref="AH44:AH66" si="27">AD44/AG44</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI44" s="16"/>
@@ -11629,7 +11631,7 @@
         <v>325</v>
       </c>
       <c r="L45" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>69</v>
       </c>
       <c r="M45" s="16"/>
@@ -11638,23 +11640,23 @@
         <v>480</v>
       </c>
       <c r="P45" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>78.8</v>
       </c>
       <c r="Q45" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>141.20000000000005</v>
       </c>
       <c r="R45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>120</v>
       </c>
       <c r="S45" s="16">
-        <f>(F45+O45+R45)/P45</f>
+        <f t="shared" si="20"/>
         <v>13.730964467005077</v>
       </c>
       <c r="T45" s="16">
-        <f>(F45+O45)/P45</f>
+        <f t="shared" si="21"/>
         <v>12.208121827411167</v>
       </c>
       <c r="U45" s="16">
@@ -11677,7 +11679,7 @@
       </c>
       <c r="AA45" s="16"/>
       <c r="AB45" s="16">
-        <f>G45*Q45</f>
+        <f t="shared" si="24"/>
         <v>98.840000000000032</v>
       </c>
       <c r="AC45" s="6">
@@ -11685,11 +11687,11 @@
         <v>10</v>
       </c>
       <c r="AD45" s="8">
-        <f>MROUND(Q45, AC45*AF45)/AC45</f>
+        <f t="shared" si="25"/>
         <v>12</v>
       </c>
       <c r="AE45" s="16">
-        <f>AD45*AC45*G45</f>
+        <f t="shared" si="26"/>
         <v>84</v>
       </c>
       <c r="AF45" s="16">
@@ -11701,7 +11703,7 @@
         <v>84</v>
       </c>
       <c r="AH45" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI45" s="16"/>
@@ -11722,7 +11724,7 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>38</v>
@@ -11754,7 +11756,7 @@
         <v>100</v>
       </c>
       <c r="L46" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-24</v>
       </c>
       <c r="M46" s="16"/>
@@ -11763,20 +11765,20 @@
         <v>240</v>
       </c>
       <c r="P46" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>15.2</v>
       </c>
       <c r="Q46" s="4"/>
       <c r="R46" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S46" s="16">
-        <f>(F46+O46+R46)/P46</f>
+        <f t="shared" si="20"/>
         <v>15.657894736842106</v>
       </c>
       <c r="T46" s="16">
-        <f>(F46+O46)/P46</f>
+        <f t="shared" si="21"/>
         <v>15.657894736842106</v>
       </c>
       <c r="U46" s="16">
@@ -11799,7 +11801,7 @@
       </c>
       <c r="AA46" s="16"/>
       <c r="AB46" s="16">
-        <f>G46*Q46</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC46" s="6">
@@ -11807,11 +11809,11 @@
         <v>10</v>
       </c>
       <c r="AD46" s="8">
-        <f>MROUND(Q46, AC46*AF46)/AC46</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE46" s="16">
-        <f>AD46*AC46*G46</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF46" s="16">
@@ -11823,7 +11825,7 @@
         <v>84</v>
       </c>
       <c r="AH46" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AI46" s="16"/>
@@ -11844,7 +11846,7 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B47" s="16" t="s">
         <v>38</v>
@@ -11876,7 +11878,7 @@
         <v>646</v>
       </c>
       <c r="L47" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-17</v>
       </c>
       <c r="M47" s="16"/>
@@ -11885,23 +11887,23 @@
         <v>360</v>
       </c>
       <c r="P47" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>125.8</v>
       </c>
       <c r="Q47" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>973.2</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>960</v>
       </c>
       <c r="S47" s="16">
-        <f>(F47+O47+R47)/P47</f>
+        <f t="shared" si="20"/>
         <v>13.895071542130365</v>
       </c>
       <c r="T47" s="16">
-        <f>(F47+O47)/P47</f>
+        <f t="shared" si="21"/>
         <v>6.2639109697933231</v>
       </c>
       <c r="U47" s="16">
@@ -11924,7 +11926,7 @@
       </c>
       <c r="AA47" s="16"/>
       <c r="AB47" s="16">
-        <f>G47*Q47</f>
+        <f t="shared" si="24"/>
         <v>973.2</v>
       </c>
       <c r="AC47" s="6">
@@ -11932,11 +11934,11 @@
         <v>5</v>
       </c>
       <c r="AD47" s="8">
-        <f>MROUND(Q47, AC47*AF47)/AC47</f>
+        <f t="shared" si="25"/>
         <v>192</v>
       </c>
       <c r="AE47" s="16">
-        <f>AD47*AC47*G47</f>
+        <f t="shared" si="26"/>
         <v>960</v>
       </c>
       <c r="AF47" s="16">
@@ -11948,7 +11950,7 @@
         <v>84</v>
       </c>
       <c r="AH47" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>2.2857142857142856</v>
       </c>
       <c r="AI47" s="16"/>
@@ -11969,7 +11971,7 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>38</v>
@@ -12003,7 +12005,7 @@
         <v>193</v>
       </c>
       <c r="L48" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-12</v>
       </c>
       <c r="M48" s="16"/>
@@ -12012,23 +12014,23 @@
         <v>288</v>
       </c>
       <c r="P48" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>36.200000000000003</v>
       </c>
       <c r="Q48" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>123.80000000000007</v>
       </c>
       <c r="R48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>96</v>
       </c>
       <c r="S48" s="16">
-        <f>(F48+O48+R48)/P48</f>
+        <f t="shared" si="20"/>
         <v>13.232044198895027</v>
       </c>
       <c r="T48" s="16">
-        <f>(F48+O48)/P48</f>
+        <f t="shared" si="21"/>
         <v>10.580110497237568</v>
       </c>
       <c r="U48" s="16">
@@ -12051,7 +12053,7 @@
       </c>
       <c r="AA48" s="16"/>
       <c r="AB48" s="16">
-        <f>G48*Q48</f>
+        <f t="shared" si="24"/>
         <v>111.42000000000006</v>
       </c>
       <c r="AC48" s="6">
@@ -12059,11 +12061,11 @@
         <v>8</v>
       </c>
       <c r="AD48" s="8">
-        <f>MROUND(Q48, AC48*AF48)/AC48</f>
+        <f t="shared" si="25"/>
         <v>12</v>
       </c>
       <c r="AE48" s="16">
-        <f>AD48*AC48*G48</f>
+        <f t="shared" si="26"/>
         <v>86.4</v>
       </c>
       <c r="AF48" s="16">
@@ -12075,7 +12077,7 @@
         <v>84</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI48" s="16"/>
@@ -12096,7 +12098,7 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>38</v>
@@ -12128,7 +12130,7 @@
         <v>86</v>
       </c>
       <c r="L49" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-7</v>
       </c>
       <c r="M49" s="16"/>
@@ -12137,7 +12139,7 @@
         <v>96</v>
       </c>
       <c r="P49" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>15.8</v>
       </c>
       <c r="Q49" s="4">
@@ -12145,15 +12147,15 @@
         <v>55.800000000000011</v>
       </c>
       <c r="R49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>96</v>
       </c>
       <c r="S49" s="16">
-        <f>(F49+O49+R49)/P49</f>
+        <f t="shared" si="20"/>
         <v>18.544303797468352</v>
       </c>
       <c r="T49" s="16">
-        <f>(F49+O49)/P49</f>
+        <f t="shared" si="21"/>
         <v>12.468354430379746</v>
       </c>
       <c r="U49" s="16">
@@ -12176,7 +12178,7 @@
       </c>
       <c r="AA49" s="16"/>
       <c r="AB49" s="16">
-        <f>G49*Q49</f>
+        <f t="shared" si="24"/>
         <v>50.220000000000013</v>
       </c>
       <c r="AC49" s="6">
@@ -12184,11 +12186,11 @@
         <v>8</v>
       </c>
       <c r="AD49" s="8">
-        <f>MROUND(Q49, AC49*AF49)/AC49</f>
+        <f t="shared" si="25"/>
         <v>12</v>
       </c>
       <c r="AE49" s="16">
-        <f>AD49*AC49*G49</f>
+        <f t="shared" si="26"/>
         <v>86.4</v>
       </c>
       <c r="AF49" s="16">
@@ -12200,7 +12202,7 @@
         <v>84</v>
       </c>
       <c r="AH49" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AI49" s="16"/>
@@ -12221,10 +12223,10 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" s="16">
         <v>575</v>
@@ -12253,7 +12255,7 @@
         <v>330</v>
       </c>
       <c r="L50" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M50" s="16"/>
@@ -12262,23 +12264,23 @@
         <v>420</v>
       </c>
       <c r="P50" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>66</v>
       </c>
       <c r="Q50" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>259</v>
       </c>
       <c r="R50" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>240</v>
       </c>
       <c r="S50" s="16">
-        <f>(F50+O50+R50)/P50</f>
+        <f t="shared" si="20"/>
         <v>13.712121212121213</v>
       </c>
       <c r="T50" s="16">
-        <f>(F50+O50)/P50</f>
+        <f t="shared" si="21"/>
         <v>10.075757575757576</v>
       </c>
       <c r="U50" s="16">
@@ -12301,7 +12303,7 @@
       </c>
       <c r="AA50" s="16"/>
       <c r="AB50" s="16">
-        <f>G50*Q50</f>
+        <f t="shared" si="24"/>
         <v>259</v>
       </c>
       <c r="AC50" s="6">
@@ -12309,11 +12311,11 @@
         <v>5</v>
       </c>
       <c r="AD50" s="8">
-        <f>MROUND(Q50, AC50*AF50)/AC50</f>
+        <f t="shared" si="25"/>
         <v>48</v>
       </c>
       <c r="AE50" s="16">
-        <f>AD50*AC50*G50</f>
+        <f t="shared" si="26"/>
         <v>240</v>
       </c>
       <c r="AF50" s="16">
@@ -12325,7 +12327,7 @@
         <v>144</v>
       </c>
       <c r="AH50" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AI50" s="16"/>
@@ -12346,10 +12348,10 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="16">
         <v>206.5</v>
@@ -12378,7 +12380,7 @@
         <v>292</v>
       </c>
       <c r="L51" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-3.6999999999999886</v>
       </c>
       <c r="M51" s="16"/>
@@ -12387,23 +12389,23 @@
         <v>725.2</v>
       </c>
       <c r="P51" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>57.660000000000004</v>
       </c>
       <c r="Q51" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>163.83999999999997</v>
       </c>
       <c r="R51" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>155.4</v>
       </c>
       <c r="S51" s="16">
-        <f>(F51+O51+R51)/P51</f>
+        <f t="shared" si="20"/>
         <v>13.853624696496706</v>
       </c>
       <c r="T51" s="16">
-        <f>(F51+O51)/P51</f>
+        <f t="shared" si="21"/>
         <v>11.158515435310441</v>
       </c>
       <c r="U51" s="16">
@@ -12426,7 +12428,7 @@
       </c>
       <c r="AA51" s="16"/>
       <c r="AB51" s="16">
-        <f>G51*Q51</f>
+        <f t="shared" si="24"/>
         <v>163.83999999999997</v>
       </c>
       <c r="AC51" s="6">
@@ -12434,11 +12436,11 @@
         <v>3.7</v>
       </c>
       <c r="AD51" s="8">
-        <f>MROUND(Q51, AC51*AF51)/AC51</f>
+        <f t="shared" si="25"/>
         <v>42</v>
       </c>
       <c r="AE51" s="16">
-        <f>AD51*AC51*G51</f>
+        <f t="shared" si="26"/>
         <v>155.4</v>
       </c>
       <c r="AF51" s="16">
@@ -12450,7 +12452,7 @@
         <v>126</v>
       </c>
       <c r="AH51" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AI51" s="16"/>
@@ -12471,7 +12473,7 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B52" s="16" t="s">
         <v>38</v>
@@ -12486,21 +12488,21 @@
       <c r="F52" s="16">
         <v>276</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="19">
         <v>0.09</v>
       </c>
       <c r="H52" s="16">
         <v>180</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J52" s="16"/>
       <c r="K52" s="16">
         <v>542</v>
       </c>
       <c r="L52" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="M52" s="16"/>
@@ -12509,7 +12511,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>108.6</v>
       </c>
       <c r="Q52" s="4">
@@ -12517,15 +12519,15 @@
         <v>1135.8</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>1260</v>
       </c>
       <c r="S52" s="16">
-        <f>(F52+O52+R52)/P52</f>
+        <f t="shared" si="20"/>
         <v>14.14364640883978</v>
       </c>
       <c r="T52" s="16">
-        <f>(F52+O52)/P52</f>
+        <f t="shared" si="21"/>
         <v>2.541436464088398</v>
       </c>
       <c r="U52" s="16">
@@ -12547,21 +12549,21 @@
         <v>76.2</v>
       </c>
       <c r="AA52" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB52" s="16">
-        <f>G52*Q52</f>
+        <f t="shared" si="24"/>
         <v>102.22199999999999</v>
       </c>
       <c r="AC52" s="6">
         <v>30</v>
       </c>
       <c r="AD52" s="8">
-        <f>MROUND(Q52, AC52*AF52)/AC52</f>
+        <f t="shared" si="25"/>
         <v>42</v>
       </c>
       <c r="AE52" s="16">
-        <f>AD52*AC52*G52</f>
+        <f t="shared" si="26"/>
         <v>113.39999999999999</v>
       </c>
       <c r="AF52" s="16">
@@ -12571,7 +12573,7 @@
         <v>126</v>
       </c>
       <c r="AH52" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AI52" s="16"/>
@@ -12592,7 +12594,7 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>38</v>
@@ -12624,7 +12626,7 @@
         <v>92</v>
       </c>
       <c r="L53" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-18</v>
       </c>
       <c r="M53" s="16"/>
@@ -12633,20 +12635,20 @@
         <v>336</v>
       </c>
       <c r="P53" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>14.8</v>
       </c>
       <c r="Q53" s="4"/>
       <c r="R53" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S53" s="16">
-        <f>(F53+O53+R53)/P53</f>
+        <f t="shared" si="20"/>
         <v>21.95945945945946</v>
       </c>
       <c r="T53" s="16">
-        <f>(F53+O53)/P53</f>
+        <f t="shared" si="21"/>
         <v>21.95945945945946</v>
       </c>
       <c r="U53" s="16">
@@ -12669,7 +12671,7 @@
       </c>
       <c r="AA53" s="16"/>
       <c r="AB53" s="16">
-        <f>G53*Q53</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC53" s="6">
@@ -12677,11 +12679,11 @@
         <v>6</v>
       </c>
       <c r="AD53" s="8">
-        <f>MROUND(Q53, AC53*AF53)/AC53</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE53" s="16">
-        <f>AD53*AC53*G53</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF53" s="16">
@@ -12693,7 +12695,7 @@
         <v>140</v>
       </c>
       <c r="AH53" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AI53" s="16"/>
@@ -12714,7 +12716,7 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>38</v>
@@ -12748,7 +12750,7 @@
         <v>715</v>
       </c>
       <c r="L54" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-69</v>
       </c>
       <c r="M54" s="16"/>
@@ -12757,23 +12759,23 @@
         <v>504</v>
       </c>
       <c r="P54" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>129.19999999999999</v>
       </c>
       <c r="Q54" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>528.79999999999973</v>
       </c>
       <c r="R54" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>504</v>
       </c>
       <c r="S54" s="16">
-        <f>(F54+O54+R54)/P54</f>
+        <f t="shared" si="20"/>
         <v>13.808049535603717</v>
       </c>
       <c r="T54" s="16">
-        <f>(F54+O54)/P54</f>
+        <f t="shared" si="21"/>
         <v>9.9071207430340564</v>
       </c>
       <c r="U54" s="16">
@@ -12796,7 +12798,7 @@
       </c>
       <c r="AA54" s="16"/>
       <c r="AB54" s="16">
-        <f>G54*Q54</f>
+        <f t="shared" si="24"/>
         <v>132.19999999999993</v>
       </c>
       <c r="AC54" s="6">
@@ -12804,11 +12806,11 @@
         <v>12</v>
       </c>
       <c r="AD54" s="8">
-        <f>MROUND(Q54, AC54*AF54)/AC54</f>
+        <f t="shared" si="25"/>
         <v>42</v>
       </c>
       <c r="AE54" s="16">
-        <f>AD54*AC54*G54</f>
+        <f t="shared" si="26"/>
         <v>126</v>
       </c>
       <c r="AF54" s="16">
@@ -12820,7 +12822,7 @@
         <v>70</v>
       </c>
       <c r="AH54" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.6</v>
       </c>
       <c r="AI54" s="16"/>
@@ -12841,7 +12843,7 @@
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>38</v>
@@ -12873,7 +12875,7 @@
         <v>440</v>
       </c>
       <c r="L55" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-20</v>
       </c>
       <c r="M55" s="16"/>
@@ -12882,23 +12884,23 @@
         <v>168</v>
       </c>
       <c r="P55" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>84</v>
       </c>
       <c r="Q55" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>540</v>
       </c>
       <c r="R55" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>504</v>
       </c>
       <c r="S55" s="16">
-        <f>(F55+O55+R55)/P55</f>
+        <f t="shared" si="20"/>
         <v>13.571428571428571</v>
       </c>
       <c r="T55" s="16">
-        <f>(F55+O55)/P55</f>
+        <f t="shared" si="21"/>
         <v>7.5714285714285712</v>
       </c>
       <c r="U55" s="16">
@@ -12921,7 +12923,7 @@
       </c>
       <c r="AA55" s="16"/>
       <c r="AB55" s="16">
-        <f>G55*Q55</f>
+        <f t="shared" si="24"/>
         <v>135</v>
       </c>
       <c r="AC55" s="6">
@@ -12929,11 +12931,11 @@
         <v>12</v>
       </c>
       <c r="AD55" s="8">
-        <f>MROUND(Q55, AC55*AF55)/AC55</f>
+        <f t="shared" si="25"/>
         <v>42</v>
       </c>
       <c r="AE55" s="16">
-        <f>AD55*AC55*G55</f>
+        <f t="shared" si="26"/>
         <v>126</v>
       </c>
       <c r="AF55" s="16">
@@ -12945,7 +12947,7 @@
         <v>70</v>
       </c>
       <c r="AH55" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.6</v>
       </c>
       <c r="AI55" s="16"/>
@@ -12966,7 +12968,7 @@
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>38</v>
@@ -13000,7 +13002,7 @@
         <v>23</v>
       </c>
       <c r="L56" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-1</v>
       </c>
       <c r="M56" s="16"/>
@@ -13009,20 +13011,20 @@
         <v>0</v>
       </c>
       <c r="P56" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="Q56" s="4"/>
       <c r="R56" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S56" s="16">
-        <f>(F56+O56+R56)/P56</f>
+        <f t="shared" si="20"/>
         <v>14.318181818181817</v>
       </c>
       <c r="T56" s="16">
-        <f>(F56+O56)/P56</f>
+        <f t="shared" si="21"/>
         <v>14.318181818181817</v>
       </c>
       <c r="U56" s="16">
@@ -13045,7 +13047,7 @@
       </c>
       <c r="AA56" s="16"/>
       <c r="AB56" s="16">
-        <f>G56*Q56</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC56" s="6">
@@ -13053,11 +13055,11 @@
         <v>6</v>
       </c>
       <c r="AD56" s="8">
-        <f>MROUND(Q56, AC56*AF56)/AC56</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE56" s="16">
-        <f>AD56*AC56*G56</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF56" s="16">
@@ -13069,7 +13071,7 @@
         <v>140</v>
       </c>
       <c r="AH56" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AI56" s="16"/>
@@ -13090,7 +13092,7 @@
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>38</v>
@@ -13122,7 +13124,7 @@
         <v>28</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M57" s="16"/>
@@ -13131,20 +13133,20 @@
         <v>84</v>
       </c>
       <c r="P57" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>5.6</v>
       </c>
       <c r="Q57" s="4"/>
       <c r="R57" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S57" s="16">
-        <f>(F57+O57+R57)/P57</f>
+        <f t="shared" si="20"/>
         <v>21.964285714285715</v>
       </c>
       <c r="T57" s="16">
-        <f>(F57+O57)/P57</f>
+        <f t="shared" si="21"/>
         <v>21.964285714285715</v>
       </c>
       <c r="U57" s="16">
@@ -13167,7 +13169,7 @@
       </c>
       <c r="AA57" s="16"/>
       <c r="AB57" s="16">
-        <f>G57*Q57</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC57" s="6">
@@ -13175,11 +13177,11 @@
         <v>6</v>
       </c>
       <c r="AD57" s="8">
-        <f>MROUND(Q57, AC57*AF57)/AC57</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE57" s="16">
-        <f>AD57*AC57*G57</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF57" s="16">
@@ -13191,7 +13193,7 @@
         <v>140</v>
       </c>
       <c r="AH57" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AI57" s="16"/>
@@ -13212,7 +13214,7 @@
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>38</v>
@@ -13236,7 +13238,7 @@
       <c r="J58" s="16"/>
       <c r="K58" s="16"/>
       <c r="L58" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M58" s="16"/>
@@ -13245,20 +13247,20 @@
         <v>84</v>
       </c>
       <c r="P58" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q58" s="4"/>
       <c r="R58" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S58" s="16" t="e">
-        <f>(F58+O58+R58)/P58</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T58" s="16" t="e">
-        <f>(F58+O58)/P58</f>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U58" s="16">
@@ -13281,7 +13283,7 @@
       </c>
       <c r="AA58" s="16"/>
       <c r="AB58" s="16">
-        <f>G58*Q58</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC58" s="6">
@@ -13289,11 +13291,11 @@
         <v>6</v>
       </c>
       <c r="AD58" s="8">
-        <f>MROUND(Q58, AC58*AF58)/AC58</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE58" s="16">
-        <f>AD58*AC58*G58</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF58" s="16">
@@ -13305,7 +13307,7 @@
         <v>140</v>
       </c>
       <c r="AH58" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AI58" s="16"/>
@@ -13326,7 +13328,7 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" s="16" t="s">
         <v>38</v>
@@ -13358,7 +13360,7 @@
         <v>600</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-31</v>
       </c>
       <c r="M59" s="16"/>
@@ -13367,23 +13369,23 @@
         <v>672</v>
       </c>
       <c r="P59" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>113.8</v>
       </c>
       <c r="Q59" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>598.20000000000005</v>
       </c>
       <c r="R59" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>672</v>
       </c>
       <c r="S59" s="16">
-        <f>(F59+O59+R59)/P59</f>
+        <f t="shared" si="20"/>
         <v>14.648506151142355</v>
       </c>
       <c r="T59" s="16">
-        <f>(F59+O59)/P59</f>
+        <f t="shared" si="21"/>
         <v>8.743409490333919</v>
       </c>
       <c r="U59" s="16">
@@ -13406,7 +13408,7 @@
       </c>
       <c r="AA59" s="16"/>
       <c r="AB59" s="16">
-        <f>G59*Q59</f>
+        <f t="shared" si="24"/>
         <v>179.46</v>
       </c>
       <c r="AC59" s="6">
@@ -13414,11 +13416,11 @@
         <v>12</v>
       </c>
       <c r="AD59" s="8">
-        <f>MROUND(Q59, AC59*AF59)/AC59</f>
+        <f t="shared" si="25"/>
         <v>56</v>
       </c>
       <c r="AE59" s="16">
-        <f>AD59*AC59*G59</f>
+        <f t="shared" si="26"/>
         <v>201.6</v>
       </c>
       <c r="AF59" s="16">
@@ -13430,7 +13432,7 @@
         <v>70</v>
       </c>
       <c r="AH59" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.8</v>
       </c>
       <c r="AI59" s="16"/>
@@ -13451,7 +13453,7 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B60" s="16" t="s">
         <v>38</v>
@@ -13483,7 +13485,7 @@
         <v>535</v>
       </c>
       <c r="L60" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-39</v>
       </c>
       <c r="M60" s="16"/>
@@ -13492,23 +13494,23 @@
         <v>0</v>
       </c>
       <c r="P60" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>99.2</v>
       </c>
       <c r="Q60" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>370.79999999999995</v>
       </c>
       <c r="R60" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>336</v>
       </c>
       <c r="S60" s="16">
-        <f>(F60+O60+R60)/P60</f>
+        <f t="shared" si="20"/>
         <v>13.649193548387096</v>
       </c>
       <c r="T60" s="16">
-        <f>(F60+O60)/P60</f>
+        <f t="shared" si="21"/>
         <v>10.262096774193548</v>
       </c>
       <c r="U60" s="16">
@@ -13531,7 +13533,7 @@
       </c>
       <c r="AA60" s="16"/>
       <c r="AB60" s="16">
-        <f>G60*Q60</f>
+        <f t="shared" si="24"/>
         <v>111.23999999999998</v>
       </c>
       <c r="AC60" s="6">
@@ -13539,11 +13541,11 @@
         <v>12</v>
       </c>
       <c r="AD60" s="8">
-        <f>MROUND(Q60, AC60*AF60)/AC60</f>
+        <f t="shared" si="25"/>
         <v>28</v>
       </c>
       <c r="AE60" s="16">
-        <f>AD60*AC60*G60</f>
+        <f t="shared" si="26"/>
         <v>100.8</v>
       </c>
       <c r="AF60" s="16">
@@ -13555,7 +13557,7 @@
         <v>70</v>
       </c>
       <c r="AH60" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.4</v>
       </c>
       <c r="AI60" s="16"/>
@@ -13576,7 +13578,7 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>38</v>
@@ -13608,7 +13610,7 @@
         <v>88</v>
       </c>
       <c r="L61" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-12</v>
       </c>
       <c r="M61" s="16"/>
@@ -13617,20 +13619,20 @@
         <v>0</v>
       </c>
       <c r="P61" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>15.2</v>
       </c>
       <c r="Q61" s="4"/>
       <c r="R61" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S61" s="16">
-        <f>(F61+O61+R61)/P61</f>
+        <f t="shared" si="20"/>
         <v>18.421052631578949</v>
       </c>
       <c r="T61" s="16">
-        <f>(F61+O61)/P61</f>
+        <f t="shared" si="21"/>
         <v>18.421052631578949</v>
       </c>
       <c r="U61" s="16">
@@ -13653,7 +13655,7 @@
       </c>
       <c r="AA61" s="16"/>
       <c r="AB61" s="16">
-        <f>G61*Q61</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC61" s="6">
@@ -13661,11 +13663,11 @@
         <v>14</v>
       </c>
       <c r="AD61" s="8">
-        <f>MROUND(Q61, AC61*AF61)/AC61</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE61" s="16">
-        <f>AD61*AC61*G61</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF61" s="16">
@@ -13677,7 +13679,7 @@
         <v>70</v>
       </c>
       <c r="AH61" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AI61" s="16"/>
@@ -13698,7 +13700,7 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>38</v>
@@ -13730,7 +13732,7 @@
         <v>1619</v>
       </c>
       <c r="L62" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-569</v>
       </c>
       <c r="M62" s="16"/>
@@ -13739,23 +13741,23 @@
         <v>2520</v>
       </c>
       <c r="P62" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>210</v>
       </c>
       <c r="Q62" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>437</v>
       </c>
       <c r="R62" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>504</v>
       </c>
       <c r="S62" s="16">
-        <f>(F62+O62+R62)/P62</f>
+        <f t="shared" si="20"/>
         <v>14.31904761904762</v>
       </c>
       <c r="T62" s="16">
-        <f>(F62+O62)/P62</f>
+        <f t="shared" si="21"/>
         <v>11.919047619047619</v>
       </c>
       <c r="U62" s="16">
@@ -13778,7 +13780,7 @@
       </c>
       <c r="AA62" s="16"/>
       <c r="AB62" s="16">
-        <f>G62*Q62</f>
+        <f t="shared" si="24"/>
         <v>109.25</v>
       </c>
       <c r="AC62" s="6">
@@ -13786,11 +13788,11 @@
         <v>12</v>
       </c>
       <c r="AD62" s="8">
-        <f>MROUND(Q62, AC62*AF62)/AC62</f>
+        <f t="shared" si="25"/>
         <v>42</v>
       </c>
       <c r="AE62" s="16">
-        <f>AD62*AC62*G62</f>
+        <f t="shared" si="26"/>
         <v>126</v>
       </c>
       <c r="AF62" s="16">
@@ -13802,7 +13804,7 @@
         <v>70</v>
       </c>
       <c r="AH62" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.6</v>
       </c>
       <c r="AI62" s="16"/>
@@ -13857,7 +13859,7 @@
         <v>1635</v>
       </c>
       <c r="L63" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>43</v>
       </c>
       <c r="M63" s="16"/>
@@ -13866,23 +13868,23 @@
         <v>1344</v>
       </c>
       <c r="P63" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>335.6</v>
       </c>
       <c r="Q63" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>1510.4000000000005</v>
       </c>
       <c r="R63" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>1512</v>
       </c>
       <c r="S63" s="16">
-        <f>(F63+O63+R63)/P63</f>
+        <f t="shared" si="20"/>
         <v>14.004767580452919</v>
       </c>
       <c r="T63" s="16">
-        <f>(F63+O63)/P63</f>
+        <f t="shared" si="21"/>
         <v>9.4994040524433849</v>
       </c>
       <c r="U63" s="16">
@@ -13905,7 +13907,7 @@
       </c>
       <c r="AA63" s="16"/>
       <c r="AB63" s="16">
-        <f>G63*Q63</f>
+        <f t="shared" si="24"/>
         <v>377.60000000000014</v>
       </c>
       <c r="AC63" s="6">
@@ -13913,11 +13915,11 @@
         <v>12</v>
       </c>
       <c r="AD63" s="8">
-        <f>MROUND(Q63, AC63*AF63)/AC63</f>
+        <f t="shared" si="25"/>
         <v>126</v>
       </c>
       <c r="AE63" s="16">
-        <f>AD63*AC63*G63</f>
+        <f t="shared" si="26"/>
         <v>378</v>
       </c>
       <c r="AF63" s="16">
@@ -13929,7 +13931,7 @@
         <v>70</v>
       </c>
       <c r="AH63" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>1.8</v>
       </c>
       <c r="AI63" s="16"/>
@@ -13950,7 +13952,7 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>38</v>
@@ -13982,7 +13984,7 @@
         <v>286</v>
       </c>
       <c r="L64" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-81</v>
       </c>
       <c r="M64" s="16"/>
@@ -13991,23 +13993,23 @@
         <v>504</v>
       </c>
       <c r="P64" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>41</v>
       </c>
       <c r="Q64" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>71</v>
       </c>
       <c r="R64" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="S64" s="16">
-        <f>(F64+O64+R64)/P64</f>
+        <f t="shared" si="20"/>
         <v>14.317073170731707</v>
       </c>
       <c r="T64" s="16">
-        <f>(F64+O64)/P64</f>
+        <f t="shared" si="21"/>
         <v>12.268292682926829</v>
       </c>
       <c r="U64" s="16">
@@ -14030,7 +14032,7 @@
       </c>
       <c r="AA64" s="16"/>
       <c r="AB64" s="16">
-        <f>G64*Q64</f>
+        <f t="shared" si="24"/>
         <v>16.330000000000002</v>
       </c>
       <c r="AC64" s="6">
@@ -14038,11 +14040,11 @@
         <v>6</v>
       </c>
       <c r="AD64" s="8">
-        <f>MROUND(Q64, AC64*AF64)/AC64</f>
+        <f t="shared" si="25"/>
         <v>14</v>
       </c>
       <c r="AE64" s="16">
-        <f>AD64*AC64*G64</f>
+        <f t="shared" si="26"/>
         <v>19.32</v>
       </c>
       <c r="AF64" s="16">
@@ -14054,7 +14056,7 @@
         <v>140</v>
       </c>
       <c r="AH64" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.1</v>
       </c>
       <c r="AI64" s="16"/>
@@ -14075,10 +14077,10 @@
     </row>
     <row r="65" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C65" s="16">
         <v>115.3</v>
@@ -14105,7 +14107,7 @@
         <v>213.3</v>
       </c>
       <c r="L65" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-153.9</v>
       </c>
       <c r="M65" s="16"/>
@@ -14114,20 +14116,20 @@
         <v>378</v>
       </c>
       <c r="P65" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>11.879999999999999</v>
       </c>
       <c r="Q65" s="4"/>
       <c r="R65" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="S65" s="16">
-        <f>(F65+O65+R65)/P65</f>
+        <f t="shared" si="20"/>
         <v>31.81818181818182</v>
       </c>
       <c r="T65" s="16">
-        <f>(F65+O65)/P65</f>
+        <f t="shared" si="21"/>
         <v>31.81818181818182</v>
       </c>
       <c r="U65" s="16">
@@ -14150,7 +14152,7 @@
       </c>
       <c r="AA65" s="16"/>
       <c r="AB65" s="16">
-        <f>G65*Q65</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC65" s="6">
@@ -14158,11 +14160,11 @@
         <v>2.7</v>
       </c>
       <c r="AD65" s="8">
-        <f>MROUND(Q65, AC65*AF65)/AC65</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE65" s="16">
-        <f>AD65*AC65*G65</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AF65" s="16">
@@ -14174,7 +14176,7 @@
         <v>126</v>
       </c>
       <c r="AH65" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AI65" s="16"/>
@@ -14195,10 +14197,10 @@
     </row>
     <row r="66" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C66" s="16">
         <v>615</v>
@@ -14229,7 +14231,7 @@
         <v>745</v>
       </c>
       <c r="L66" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>-305</v>
       </c>
       <c r="M66" s="16"/>
@@ -14238,23 +14240,23 @@
         <v>1140</v>
       </c>
       <c r="P66" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>88</v>
       </c>
       <c r="Q66" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>97</v>
       </c>
       <c r="R66" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>120</v>
       </c>
       <c r="S66" s="16">
-        <f>(F66+O66+R66)/P66</f>
+        <f t="shared" si="20"/>
         <v>14.261363636363637</v>
       </c>
       <c r="T66" s="16">
-        <f>(F66+O66)/P66</f>
+        <f t="shared" si="21"/>
         <v>12.897727272727273</v>
       </c>
       <c r="U66" s="16">
@@ -14277,7 +14279,7 @@
       </c>
       <c r="AA66" s="16"/>
       <c r="AB66" s="16">
-        <f>G66*Q66</f>
+        <f t="shared" si="24"/>
         <v>97</v>
       </c>
       <c r="AC66" s="6">
@@ -14285,11 +14287,11 @@
         <v>5</v>
       </c>
       <c r="AD66" s="8">
-        <f>MROUND(Q66, AC66*AF66)/AC66</f>
+        <f t="shared" si="25"/>
         <v>24</v>
       </c>
       <c r="AE66" s="16">
-        <f>AD66*AC66*G66</f>
+        <f t="shared" si="26"/>
         <v>120</v>
       </c>
       <c r="AF66" s="16">
@@ -14301,7 +14303,7 @@
         <v>84</v>
       </c>
       <c r="AH66" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="27"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AI66" s="16"/>
@@ -14322,10 +14324,10 @@
     </row>
     <row r="67" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C67" s="12">
         <v>-5</v>
@@ -14342,31 +14344,31 @@
         <v>0</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K67" s="12"/>
       <c r="L67" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M67" s="12"/>
       <c r="N67" s="12"/>
       <c r="O67" s="12"/>
       <c r="P67" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q67" s="14"/>
       <c r="R67" s="14"/>
       <c r="S67" s="12" t="e">
-        <f>(F67+O67+R67)/P67</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T67" s="12" t="e">
-        <f>(F67+O67)/P67</f>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U67" s="12">
